--- a/Avaliação_Binarização.xlsx
+++ b/Avaliação_Binarização.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/449a581fa2a8fcc8/Área de Trabalho/Pastas/IPI/tf_ipi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90C67B58-89C6-482F-B129-F77FB4C5E726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{90C67B58-89C6-482F-B129-F77FB4C5E726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36EAD0C0-3546-45E6-9CE3-3516E469152F}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="2100" windowWidth="15375" windowHeight="7875" xr2:uid="{156C95D9-43B2-4197-95B1-9198BA43134C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{156C95D9-43B2-4197-95B1-9198BA43134C}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>Método</t>
+  </si>
   <si>
     <t>FM</t>
   </si>
@@ -47,6 +50,12 @@
     <t>DRD</t>
   </si>
   <si>
+    <t>Otsu</t>
+  </si>
+  <si>
+    <t>Mitianoudis</t>
+  </si>
+  <si>
     <t>Imagem</t>
   </si>
   <si>
@@ -90,6 +99,21 @@
   </si>
   <si>
     <t>Av.N-DRD</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Boudra</t>
+  </si>
+  <si>
+    <t>Sauvola</t>
+  </si>
+  <si>
+    <t>Nick</t>
+  </si>
+  <si>
+    <t>Niblack</t>
   </si>
 </sst>
 </file>
@@ -151,6 +175,219 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>173934</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>14927</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>183779</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{665B2A50-AC7C-B072-9C6A-5B154AF1281A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2840934"/>
+          <a:ext cx="3096057" cy="2295845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E61015-414A-0207-C541-3875EC384220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3695700" y="2857500"/>
+          <a:ext cx="3095625" cy="2295525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagem 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51DEC607-A772-F3B3-3322-80DD1FC1EC93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4305300" y="6286500"/>
+          <a:ext cx="3076575" cy="1343025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91919469-E8A3-4F02-A548-A2C0F92CF52A}" name="Tabela1" displayName="Tabela1" ref="A1:E12" totalsRowShown="0">
+  <autoFilter ref="A1:E12" xr:uid="{91919469-E8A3-4F02-A548-A2C0F92CF52A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{ADF5CC8F-72C8-42EE-99CE-A84BA52BD65E}" name="Imagem"/>
+    <tableColumn id="2" xr3:uid="{7A08D677-4EF3-4022-BDC0-1FB35AAC0228}" name="FM"/>
+    <tableColumn id="3" xr3:uid="{9C366623-040C-47AC-9823-DB6BE875151E}" name="PFM"/>
+    <tableColumn id="4" xr3:uid="{789D4630-85C6-45EB-8A71-29E1F6D0E44A}" name="PSNR"/>
+    <tableColumn id="5" xr3:uid="{648BD765-074E-44C8-8032-29E8E4B3B56E}" name="DRD"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1E068482-F17C-49FC-BF85-04589EE5E063}" name="Tabela2" displayName="Tabela2" ref="F1:J12" totalsRowShown="0">
+  <autoFilter ref="F1:J12" xr:uid="{1E068482-F17C-49FC-BF85-04589EE5E063}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{5D7E468C-69FF-4CE4-912A-A0447ADC5B25}" name="Imagem"/>
+    <tableColumn id="2" xr3:uid="{668E59EE-86C5-40EE-B04B-AFBDE3AD016E}" name="N-FM"/>
+    <tableColumn id="3" xr3:uid="{39E0002D-95EF-45BD-B768-9622837AB50D}" name="N-PFM"/>
+    <tableColumn id="4" xr3:uid="{748B7F80-6EAD-4CBF-90D0-16A297BBAF11}" name="N-PSNR"/>
+    <tableColumn id="5" xr3:uid="{DD0272DA-18A1-43B1-A8C4-A64F244E4E2A}" name="N-DRD"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F2EFCA00-AA7B-456B-B41C-4B1B669E8CAD}" name="Tabela3" displayName="Tabela3" ref="A29:E35" totalsRowShown="0">
+  <autoFilter ref="A29:E35" xr:uid="{F2EFCA00-AA7B-456B-B41C-4B1B669E8CAD}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{19E7BD1E-711A-47FE-8FFB-8DB1AE22A9A5}" name="Método"/>
+    <tableColumn id="2" xr3:uid="{7A67B342-E612-4AEE-ACAD-62C8B9807CD5}" name="FM"/>
+    <tableColumn id="3" xr3:uid="{A72FD11E-5BE2-4C08-8749-57E69FB943C8}" name="PFM"/>
+    <tableColumn id="4" xr3:uid="{C7ACC1C6-F115-4873-A91F-6810895026DF}" name="PSNR"/>
+    <tableColumn id="5" xr3:uid="{43F3B8E6-8C1B-4C3C-8C35-9BA6421B257B}" name="DRD"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -470,60 +707,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC6E916-61F8-40D8-A51D-A87ED68D098C}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -543,15 +788,18 @@
         <v>1.9052</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>88.718699999999998</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>98.246099999999998</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>19.3522</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>2.8035000000000001</v>
       </c>
       <c r="K2">
@@ -559,7 +807,7 @@
         <v>92.01400000000001</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:R2" si="0">AVERAGE(C2:C11)</f>
+        <f t="shared" ref="L2:N2" si="0">AVERAGE(C2:C11)</f>
         <v>95.532859999999999</v>
       </c>
       <c r="M2">
@@ -571,19 +819,19 @@
         <v>2.4998800000000001</v>
       </c>
       <c r="O2">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(G2:G11)</f>
         <v>79.76294</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(H2:H11)</f>
         <v>83.921530000000004</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(I2:I11)</f>
         <v>15.65001</v>
       </c>
       <c r="R2">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(J2:J11)</f>
         <v>7.4948300000000003</v>
       </c>
     </row>
@@ -604,15 +852,18 @@
         <v>3.7307999999999999</v>
       </c>
       <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>86.661900000000003</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>93.302800000000005</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>17.102799999999998</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3.7726999999999999</v>
       </c>
       <c r="K3">
@@ -620,7 +871,7 @@
         <v>3.9341266722531092</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:R3" si="1">_xlfn.STDEV.S(C2:C11)</f>
+        <f t="shared" ref="L3:N3" si="1">_xlfn.STDEV.S(C2:C11)</f>
         <v>4.3584021443133922</v>
       </c>
       <c r="M3">
@@ -632,19 +883,19 @@
         <v>1.3683074945185223</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(G2:G11)</f>
         <v>15.277107836760209</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(H2:H11)</f>
         <v>20.498215929958899</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(I2:I11)</f>
         <v>3.6918400875594672</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(J2:J11)</f>
         <v>6.5269954503584566</v>
       </c>
     </row>
@@ -665,15 +916,18 @@
         <v>1.31</v>
       </c>
       <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>76.923400000000001</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>74.888999999999996</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>14.0816</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>15.014699999999999</v>
       </c>
     </row>
@@ -694,15 +948,18 @@
         <v>1.7577</v>
       </c>
       <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
         <v>75.993200000000002</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>75.570099999999996</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>12.3254</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>9.1198999999999995</v>
       </c>
     </row>
@@ -723,15 +980,18 @@
         <v>2.1928999999999998</v>
       </c>
       <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
         <v>79.101699999999994</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>82.4328</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>12.4739</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>8.2997999999999994</v>
       </c>
     </row>
@@ -752,15 +1012,18 @@
         <v>2.6490999999999998</v>
       </c>
       <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <v>38.727600000000002</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>31.353100000000001</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>9.3308999999999997</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>22.3401</v>
       </c>
     </row>
@@ -781,15 +1044,18 @@
         <v>5.8971</v>
       </c>
       <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>86.746899999999997</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>95.484300000000005</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>16.6371</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>3.5718000000000001</v>
       </c>
     </row>
@@ -810,15 +1076,18 @@
         <v>1.6093999999999999</v>
       </c>
       <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
         <v>88.720699999999994</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>96.913399999999996</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>22.012699999999999</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>3.0392000000000001</v>
       </c>
     </row>
@@ -839,15 +1108,18 @@
         <v>2.0432999999999999</v>
       </c>
       <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
         <v>88.650499999999994</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>95.860900000000001</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>16.799900000000001</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>3.3121999999999998</v>
       </c>
     </row>
@@ -868,20 +1140,180 @@
         <v>1.9033</v>
       </c>
       <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
         <v>87.384799999999998</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>95.162800000000004</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>16.383600000000001</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>3.6743999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>92.01400000000001</v>
+      </c>
+      <c r="C12">
+        <v>95.532859999999999</v>
+      </c>
+      <c r="D12">
+        <v>18.883349999999997</v>
+      </c>
+      <c r="E12">
+        <v>2.4998800000000001</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>79.76294</v>
+      </c>
+      <c r="H12">
+        <v>83.921530000000004</v>
+      </c>
+      <c r="I12">
+        <v>15.65001</v>
+      </c>
+      <c r="J12">
+        <v>7.4948300000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30">
+        <v>92.4</v>
+      </c>
+      <c r="C30">
+        <v>96.46</v>
+      </c>
+      <c r="D30">
+        <v>19.09</v>
+      </c>
+      <c r="E30">
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>91.63</v>
+      </c>
+      <c r="C31">
+        <v>95.5</v>
+      </c>
+      <c r="D31">
+        <v>18.71</v>
+      </c>
+      <c r="E31">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>89.77</v>
+      </c>
+      <c r="C32">
+        <v>90.98</v>
+      </c>
+      <c r="D32">
+        <v>18.46</v>
+      </c>
+      <c r="E32">
+        <v>4.2270000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>86.83</v>
+      </c>
+      <c r="C33">
+        <v>91.8</v>
+      </c>
+      <c r="D33">
+        <v>17.63</v>
+      </c>
+      <c r="E33">
+        <v>4.8959999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34">
+        <v>87.8</v>
+      </c>
+      <c r="C34">
+        <v>90.5</v>
+      </c>
+      <c r="D34">
+        <v>17.59</v>
+      </c>
+      <c r="E34">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35">
+        <v>45.49</v>
+      </c>
+      <c r="C35">
+        <v>46.03</v>
+      </c>
+      <c r="D35">
+        <v>6.72</v>
+      </c>
+      <c r="E35">
+        <v>72.95</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="3">
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>